--- a/Project2348_D.Cusco(2025).xlsx
+++ b/Project2348_D.Cusco(2025).xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\domin\Downloads\Desktop\Year 3\diss\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\neotrans\inst\matrices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{49B100DB-4F92-4268-BD7A-1DE277A367CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADB0FAA7-8556-4081-B2D1-9CA26A8519B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{5AC7AADF-1455-4A1C-A2C0-0B7B2C18B243}"/>
   </bookViews>
@@ -197,7 +197,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="106">
   <si>
     <t>Charlabels</t>
   </si>
@@ -505,26 +505,23 @@
     <t>NT?;0=0-;1=11;2=12;3=13;4=0-</t>
   </si>
   <si>
-    <t>NT?;0=0-;1=11;2=12;3=13;4=14;5=15;6=16;7=17</t>
-  </si>
-  <si>
-    <t>NT?;0=11;1=12;2=0-</t>
-  </si>
-  <si>
-    <t>NT?;0=0-;1=11;2=12</t>
-  </si>
-  <si>
     <t>NT2;0=0-;1=11;2=12</t>
   </si>
   <si>
-    <t>NT?;0=1-;1=11;2=12</t>
+    <t>NT?;0=0-;1=11;2=12;3=12;4=12;5=12;6=12</t>
+  </si>
+  <si>
+    <t>NT2;0=12;1=11;2=0-</t>
+  </si>
+  <si>
+    <t>NT2;0=1-;1=11;2=12</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -560,12 +557,6 @@
       <name val="Tahoma"/>
       <family val="2"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -593,7 +584,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -609,10 +600,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1157,6 +1144,9 @@
       <c r="B16" t="s">
         <v>101</v>
       </c>
+      <c r="D16" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
@@ -1373,7 +1363,10 @@
         <v>34</v>
       </c>
       <c r="B32" t="s">
-        <v>102</v>
+        <v>103</v>
+      </c>
+      <c r="D32" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.35">
@@ -1605,7 +1598,10 @@
         <v>51</v>
       </c>
       <c r="B49" t="s">
-        <v>103</v>
+        <v>104</v>
+      </c>
+      <c r="D49" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.35">
@@ -1627,7 +1623,10 @@
         <v>53</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
+      </c>
+      <c r="D51" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.35">
@@ -1999,7 +1998,10 @@
         <v>80</v>
       </c>
       <c r="B78" t="s">
-        <v>105</v>
+        <v>102</v>
+      </c>
+      <c r="D78" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.35">
@@ -2049,7 +2051,10 @@
         <v>84</v>
       </c>
       <c r="B82" t="s">
-        <v>106</v>
+        <v>105</v>
+      </c>
+      <c r="D82" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.35">
